--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -163,147 +163,129 @@
     <x:t>35</x:t>
   </x:si>
   <x:si>
-    <x:t>H0WA08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
+    <x:t>H2FL14053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0GA14030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA10175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX10221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4NH02399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S0SC00149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6WY00209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OK04247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4AR02141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0MI02094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2GA01157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6LA00664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6WA04216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
   </x:si>
   <x:si>
     <x:t>WA</x:t>
   </x:si>
   <x:si>
-    <x:t>H2FL14053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0GA14030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA10175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX10221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4NH02399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODLANDER, MAGGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S0SC00149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6WY00209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6OK04247</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4AR02141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0MI02094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2GA01157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA01109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6LA00664</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6WA04216</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6MI13254</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX09140</x:t>
   </x:si>
   <x:si>
@@ -391,12 +373,6 @@
     <x:t>SD</x:t>
   </x:si>
   <x:si>
-    <x:t>H8WA08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCHRIER, KIM DR.</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX19206</x:t>
   </x:si>
   <x:si>
@@ -415,31 +391,10 @@
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>H8AZ09040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STANTON, GREG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX08209</x:t>
   </x:si>
   <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0WA10034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2MI13204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
   </x:si>
   <x:si>
     <x:t>H8SC04250</x:t>
@@ -537,8 +492,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J50" totalsRowShown="0">
-  <x:autoFilter ref="A1:J50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J44" totalsRowShown="0">
+  <x:autoFilter ref="A1:J44"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -843,7 +798,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J50"/>
+  <x:dimension ref="A1:J44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1196,13 +1151,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>113120</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1213,28 +1168,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>151713</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1245,28 +1200,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>455146</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1277,10 +1232,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>56</x:v>
@@ -1298,7 +1253,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>300000</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1324,13 +1279,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>708827</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1341,28 +1296,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>91656</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1379,22 +1334,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>150000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1405,10 +1360,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>68</x:v>
@@ -1426,7 +1381,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>550000</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1458,7 +1413,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>515838</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1469,16 +1424,16 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>30</x:v>
@@ -1487,10 +1442,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>735613</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1501,10 +1456,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>74</x:v>
@@ -1513,16 +1468,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>300000</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1548,13 +1503,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>418060</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1580,13 +1535,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>511996</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1603,10 +1558,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
@@ -1629,28 +1584,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="H25" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1661,10 +1616,10 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>87</x:v>
@@ -1673,16 +1628,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>350000</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1708,13 +1663,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>506917</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1731,54 +1686,54 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>268690</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>461943</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1789,10 +1744,10 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>99</x:v>
@@ -1804,13 +1759,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="H30" s="1">
-        <x:v>34890</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1821,16 +1776,16 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>30</x:v>
@@ -1839,10 +1794,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>250000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1853,28 +1808,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>400022</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1891,22 +1846,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>12203100</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1923,10 +1878,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>30</x:v>
@@ -1935,10 +1890,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1955,22 +1910,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>80948</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1987,10 +1942,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>30</x:v>
@@ -1999,10 +1954,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>221403</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2013,28 +1968,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H37" s="1">
-        <x:v>141263</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2045,16 +2000,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>118</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>30</x:v>
@@ -2063,10 +2018,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>2250000</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2077,10 +2032,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>119</x:v>
@@ -2089,16 +2044,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>350000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2121,16 +2076,16 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>411748</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2141,10 +2096,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>125</x:v>
@@ -2156,13 +2111,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>105040</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2188,13 +2143,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>426280</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2205,28 +2160,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
+      <x:c r="G43" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
       <x:c r="H43" s="1">
-        <x:v>282975</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2237,10 +2192,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>133</x:v>
@@ -2249,213 +2204,21 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>157560</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:10">
-      <x:c r="A45" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H45" s="1">
-        <x:v>771658</x:v>
-      </x:c>
-      <x:c r="I45" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J45" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:10">
-      <x:c r="A46" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G46" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H46" s="1">
-        <x:v>103020</x:v>
-      </x:c>
-      <x:c r="I46" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J46" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:10">
-      <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G47" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H47" s="1">
-        <x:v>1762153</x:v>
-      </x:c>
-      <x:c r="I47" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J47" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:10">
-      <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H48" s="1">
-        <x:v>487317</x:v>
-      </x:c>
-      <x:c r="I48" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J48" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:10">
-      <x:c r="A49" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H49" s="1">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="I49" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J49" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:10">
-      <x:c r="A50" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G50" s="1" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H50" s="1">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="I50" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J50" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -133,6 +133,18 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
+    <x:t>S6OH00163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BROWN, SHERROD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0AL01055</x:t>
   </x:si>
   <x:si>
@@ -254,6 +266,12 @@
   </x:si>
   <x:si>
     <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OH00304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUSTED, JON</x:t>
   </x:si>
   <x:si>
     <x:t>H2GA01157</x:t>
@@ -492,8 +510,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J44" totalsRowShown="0">
-  <x:autoFilter ref="A1:J44"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J46" totalsRowShown="0">
+  <x:autoFilter ref="A1:J46"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -798,7 +816,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J44"/>
+  <x:dimension ref="A1:J46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1052,30 +1070,30 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G8" s="1" t="s">
+      <x:c r="H8" s="1">
+        <x:v>5731065</x:v>
+      </x:c>
+      <x:c r="I8" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J8" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="H8" s="1">
-        <x:v>547042</x:v>
-      </x:c>
-      <x:c r="I8" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J8" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>43</x:v>
@@ -1084,16 +1102,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>350000</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1104,28 +1122,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>616386</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1136,28 +1154,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>151713</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1168,10 +1186,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>53</x:v>
@@ -1186,10 +1204,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>455146</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1200,28 +1218,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1232,28 +1250,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1270,22 +1288,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1296,28 +1314,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>150000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1340,16 +1358,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>550000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1360,16 +1378,16 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>30</x:v>
@@ -1378,10 +1396,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>515838</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1398,10 +1416,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>30</x:v>
@@ -1410,10 +1428,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>735613</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1424,16 +1442,16 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>30</x:v>
@@ -1442,10 +1460,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1456,28 +1474,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1494,22 +1512,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1526,22 +1544,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1558,22 +1576,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="H24" s="1">
-        <x:v>430866</x:v>
+        <x:v>5730541</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1584,28 +1602,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1622,22 +1640,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>506917</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1648,10 +1666,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>90</x:v>
@@ -1660,16 +1678,16 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H27" s="1">
-        <x:v>461943</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1680,10 +1698,10 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>93</x:v>
@@ -1695,13 +1713,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="H28" s="1">
-        <x:v>34890</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1712,28 +1730,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>250000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1744,10 +1762,10 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>99</x:v>
@@ -1759,13 +1777,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>400022</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1776,16 +1794,16 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>30</x:v>
@@ -1794,10 +1812,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>12203100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1808,28 +1826,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>350000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1846,22 +1864,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>80948</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1878,10 +1896,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>30</x:v>
@@ -1890,10 +1908,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1910,22 +1928,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1942,10 +1960,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>30</x:v>
@@ -1954,10 +1972,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>2250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1968,28 +1986,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2000,16 +2018,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>30</x:v>
@@ -2018,10 +2036,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>411748</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2032,10 +2050,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>119</x:v>
@@ -2044,16 +2062,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G39" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H39" s="1">
-        <x:v>426280</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2076,16 +2094,16 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>115</x:v>
-      </x:c>
       <x:c r="H40" s="1">
-        <x:v>282975</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2111,13 +2129,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>771658</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2134,22 +2152,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>487317</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2160,28 +2178,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>300000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2192,10 +2210,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>133</x:v>
@@ -2204,21 +2222,85 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H44" s="1">
+        <x:v>487317</x:v>
+      </x:c>
+      <x:c r="I44" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J44" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
+      <x:c r="A45" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H45" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I45" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J45" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
+      <x:c r="A46" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F44" s="1" t="s">
+      <x:c r="F46" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H44" s="1">
+      <x:c r="G46" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H46" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I44" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J44" s="1" t="s">
+      <x:c r="I46" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J46" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -46,325 +46,307 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8IN04199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0KY06104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6KY00286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2AK01083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX02244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OH00163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BROWN, SHERROD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0AL01055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6GA00390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX35087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0GA14030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA10175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX10221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4NH02399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S0SC00149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6WY00209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OK04247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4AR02141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0MI02094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OH00304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUSTED, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2GA01157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6GA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6LA00664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6WA04216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX09140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
     <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
-    <x:t>H0MA04192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>House</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8IN04199</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0KY06104</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6KY00286</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2AK01083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX02244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6OH00163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BROWN, SHERROD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0AL01055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6GA00390</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX35087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2FL14053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
+    <x:t>H2NJ13075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6LA00540</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0UT01205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6AL00476</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4NC14015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6KY00302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX22283</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
   </x:si>
   <x:si>
     <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0GA14030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA10175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX10221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4NH02399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODLANDER, MAGGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S0SC00149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6WY00209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6OK04247</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4AR02141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0MI02094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6OH00304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUSTED, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2GA01157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6GA01109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6LA00664</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6WA04216</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX09140</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2NJ13075</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6LA00540</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0UT01205</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6AL00476</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H4NC14015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6KY00302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6TX22283</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
   </x:si>
   <x:si>
     <x:t>S6TX00388</x:t>
@@ -510,8 +492,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J46" totalsRowShown="0">
-  <x:autoFilter ref="A1:J46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J44" totalsRowShown="0">
+  <x:autoFilter ref="A1:J44"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -816,7 +798,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J46"/>
+  <x:dimension ref="A1:J44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -887,7 +869,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>189528</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>
@@ -898,28 +880,28 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="G3" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="H3" s="1">
-        <x:v>513868</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -930,28 +912,28 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>7170138</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -962,28 +944,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="H5" s="1">
-        <x:v>628597</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -994,28 +976,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="G6" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="H6" s="1">
-        <x:v>508142</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1026,92 +1008,92 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
+      <x:c r="H7" s="1">
+        <x:v>5731065</x:v>
+      </x:c>
+      <x:c r="I7" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J7" s="1" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H7" s="1">
-        <x:v>348433</x:v>
-      </x:c>
-      <x:c r="I7" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J7" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>5731065</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>547042</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1122,28 +1104,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>350000</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1154,28 +1136,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>616386</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1186,28 +1168,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>151713</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1218,28 +1200,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>455146</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1250,28 +1232,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>300000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1282,28 +1264,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>708827</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1314,28 +1296,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>91656</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1346,28 +1328,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>150000</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1378,28 +1360,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>550000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1410,28 +1392,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>515838</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1442,28 +1424,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>735613</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1474,28 +1456,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>300000</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1506,28 +1488,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>418060</x:v>
+        <x:v>5730541</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1538,28 +1520,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>511996</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1570,28 +1552,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>5730541</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1602,28 +1584,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1634,28 +1616,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>430866</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1666,28 +1648,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>350000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1698,28 +1680,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>506917</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1730,10 +1712,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>96</x:v>
@@ -1742,16 +1724,16 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>461943</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1768,22 +1750,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="H30" s="1">
-        <x:v>34890</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1794,28 +1776,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>250000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1826,28 +1808,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>400022</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1858,28 +1840,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>12203100</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1890,28 +1872,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>350000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1922,28 +1904,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>80948</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1954,28 +1936,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>221403</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1986,28 +1968,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H37" s="1">
-        <x:v>141263</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2018,28 +2000,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="E38" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H38" s="1">
-        <x:v>2250000</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2050,10 +2032,10 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>119</x:v>
@@ -2062,16 +2044,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>350000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2082,10 +2064,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>122</x:v>
@@ -2094,16 +2076,16 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>411748</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2114,10 +2096,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>125</x:v>
@@ -2129,13 +2111,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>426280</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2146,28 +2128,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>282975</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2178,28 +2160,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="G43" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H43" s="1">
-        <x:v>771658</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2210,10 +2192,10 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
         <x:v>133</x:v>
@@ -2222,85 +2204,21 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>487317</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:10">
-      <x:c r="A45" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H45" s="1">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="I45" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J45" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:10">
-      <x:c r="A46" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G46" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H46" s="1">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="I46" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J46" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -128,6 +128,12 @@
   </x:si>
   <x:si>
     <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00911610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIGITAL FREEDOM FUND</x:t>
   </x:si>
   <x:si>
     <x:t>H0AL01055</x:t>
@@ -492,8 +498,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J44" totalsRowShown="0">
-  <x:autoFilter ref="A1:J44"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J46" totalsRowShown="0">
+  <x:autoFilter ref="A1:J46"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -798,7 +804,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J44"/>
+  <x:dimension ref="A1:J46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1040,60 +1046,60 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>547042</x:v>
+        <x:v>1485099</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="G9" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>350000</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1104,28 +1110,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="H10" s="1">
-        <x:v>616386</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1142,22 +1148,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>455146</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1168,28 +1174,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1200,28 +1206,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1238,22 +1244,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1264,10 +1270,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>56</x:v>
@@ -1279,13 +1285,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>150000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1302,22 +1308,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>550000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1328,16 +1334,16 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>25</x:v>
@@ -1346,10 +1352,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>515838</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1366,10 +1372,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>25</x:v>
@@ -1378,10 +1384,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>735613</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1392,16 +1398,16 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>25</x:v>
@@ -1410,10 +1416,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1424,28 +1430,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1462,22 +1468,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="H21" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1494,22 +1500,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>5730541</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1532,16 +1538,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>430866</x:v>
+        <x:v>5730541</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1552,28 +1558,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>430866</x:v>
+        <x:v>1485099</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1584,28 +1590,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1622,22 +1628,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>506917</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1648,28 +1654,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>461943</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1680,28 +1686,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>34890</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1712,28 +1718,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>250000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1744,28 +1750,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>400022</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1776,16 +1782,16 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>25</x:v>
@@ -1794,10 +1800,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>12203100</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1808,28 +1814,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
+      <x:c r="E32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G32" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="H32" s="1">
-        <x:v>350000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1852,16 +1858,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>80948</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1878,10 +1884,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>25</x:v>
@@ -1890,10 +1896,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>221403</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1910,22 +1916,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>141263</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1942,10 +1948,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>25</x:v>
@@ -1954,10 +1960,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>2250000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1968,28 +1974,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2000,16 +2006,16 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>25</x:v>
@@ -2018,10 +2024,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>411748</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2032,28 +2038,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>426280</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2070,22 +2076,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>282975</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2102,22 +2108,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>771658</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2134,22 +2140,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>487317</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2160,28 +2166,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>300000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2192,33 +2198,97 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G44" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H44" s="1">
+        <x:v>487317</x:v>
+      </x:c>
+      <x:c r="I44" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J44" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
+      <x:c r="A45" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B44" s="1" t="s">
+      <x:c r="B45" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C44" s="1" t="s">
+      <x:c r="C45" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="G45" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
+      <x:c r="H45" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I45" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J45" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
+      <x:c r="A46" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F44" s="1" t="s">
+      <x:c r="F46" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H44" s="1">
+      <x:c r="G46" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H46" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I44" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J44" s="1" t="s">
+      <x:c r="I46" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J46" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -46,6 +46,30 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00911610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIGITAL FREEDOM FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6IA00314</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENHOLZ, ASHLEY HINSON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -67,9 +91,6 @@
     <x:t>IN</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>H0KY06104</x:t>
   </x:si>
   <x:si>
@@ -91,12 +112,6 @@
     <x:t>S6KY00286</x:t>
   </x:si>
   <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>H2AK01083</x:t>
   </x:si>
   <x:si>
@@ -130,12 +145,6 @@
     <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
-    <x:t>C00911610</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIGITAL FREEDOM FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>H0AL01055</x:t>
   </x:si>
   <x:si>
@@ -419,6 +428,12 @@
   </x:si>
   <x:si>
     <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6IA00298</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUREK, JOSHUA</x:t>
   </x:si>
   <x:si>
     <x:t>S6VA00093</x:t>
@@ -498,8 +513,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J46" totalsRowShown="0">
-  <x:autoFilter ref="A1:J46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
+  <x:autoFilter ref="A1:J48"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -804,7 +819,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J46"/>
+  <x:dimension ref="A1:J48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -875,7 +890,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>513868</x:v>
+        <x:v>69725</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>
@@ -886,28 +901,28 @@
     </x:row>
     <x:row r="3" spans="1:10">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>7170138</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -918,28 +933,28 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>628597</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -950,28 +965,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>508142</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -982,28 +997,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>348433</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1014,66 +1029,66 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>5731065</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>1485099</x:v>
+        <x:v>5731065</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
@@ -1084,54 +1099,54 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H9" s="1">
+        <x:v>1485099</x:v>
+      </x:c>
+      <x:c r="I9" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H9" s="1">
-        <x:v>547042</x:v>
-      </x:c>
-      <x:c r="I9" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>350000</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1142,10 +1157,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>47</x:v>
@@ -1157,13 +1172,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>616386</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1174,10 +1189,10 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>50</x:v>
@@ -1186,16 +1201,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>455146</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1206,28 +1221,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1238,10 +1253,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>53</x:v>
@@ -1250,16 +1265,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1270,10 +1285,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>56</x:v>
@@ -1282,16 +1297,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1302,28 +1317,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>150000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1334,28 +1349,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>550000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1366,10 +1381,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>65</x:v>
@@ -1378,16 +1393,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>515838</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1398,10 +1413,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>68</x:v>
@@ -1410,16 +1425,16 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>735613</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1430,28 +1445,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1462,10 +1477,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>71</x:v>
@@ -1477,13 +1492,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1494,10 +1509,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>74</x:v>
@@ -1506,16 +1521,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1526,10 +1541,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>77</x:v>
@@ -1538,16 +1553,16 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>5730541</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1558,28 +1573,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>1485099</x:v>
+        <x:v>5730541</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1596,22 +1611,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>430866</x:v>
+        <x:v>1485099</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1622,25 +1637,25 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H26" s="1">
         <x:v>430866</x:v>
@@ -1654,28 +1669,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1686,10 +1701,10 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>86</x:v>
@@ -1707,7 +1722,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>506917</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1718,10 +1733,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>89</x:v>
@@ -1730,16 +1745,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="H29" s="1">
-        <x:v>461943</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1750,28 +1765,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
+      <x:c r="D30" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>34890</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1782,28 +1797,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>250000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1814,28 +1829,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>400022</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1846,10 +1861,10 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>103</x:v>
@@ -1858,16 +1873,16 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>12203100</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1878,28 +1893,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>350000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1910,28 +1925,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1942,10 +1957,10 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>108</x:v>
@@ -1954,16 +1969,16 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>221403</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1974,28 +1989,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>141263</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2006,10 +2021,10 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>113</x:v>
@@ -2018,16 +2033,16 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2038,28 +2053,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2070,10 +2085,10 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>118</x:v>
@@ -2082,16 +2097,16 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2102,10 +2117,10 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>121</x:v>
@@ -2117,13 +2132,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="H41" s="1">
-        <x:v>426280</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2134,10 +2149,10 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>124</x:v>
@@ -2146,16 +2161,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>282975</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2166,10 +2181,10 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
         <x:v>127</x:v>
@@ -2178,16 +2193,16 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2198,28 +2213,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>487317</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2230,28 +2245,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2262,33 +2277,97 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="s">
+      <x:c r="E46" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="H46" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I46" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J46" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:10">
+      <x:c r="A47" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G47" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H47" s="1">
+        <x:v>348625</x:v>
+      </x:c>
+      <x:c r="I47" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J47" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
+      <x:c r="A48" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I46" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J46" s="1" t="s">
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1594,7 +1594,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>5730541</x:v>
+        <x:v>17851755</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1594,7 +1594,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>17851755</x:v>
+        <x:v>18060379</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -145,6 +145,24 @@
     <x:t>OPPOSE</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4OR05304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYNUM, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0AL01055</x:t>
   </x:si>
   <x:si>
@@ -247,6 +265,15 @@
     <x:t>AR</x:t>
   </x:si>
   <x:si>
+    <x:t>H2NV04011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HORSFORD, STEVEN ALEXZANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NV</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0MI02094</x:t>
   </x:si>
   <x:si>
@@ -406,6 +433,15 @@
     <x:t>03</x:t>
   </x:si>
   <x:si>
+    <x:t>H8WI01156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEIL, BRYAN GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WI</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX08209</x:t>
   </x:si>
   <x:si>
@@ -428,6 +464,18 @@
   </x:si>
   <x:si>
     <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4CA45170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRAN, DEREK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
   </x:si>
   <x:si>
     <x:t>S6IA00298</x:t>
@@ -513,8 +561,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J48" totalsRowShown="0">
-  <x:autoFilter ref="A1:J48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J54" totalsRowShown="0">
+  <x:autoFilter ref="A1:J54"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -819,14 +867,14 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J48"/>
+  <x:dimension ref="A1:J54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="14.853482" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="29.424911" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="30.996339" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="17.853482" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="25.282054" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="23.424911" style="1" customWidth="1"/>
@@ -1125,28 +1173,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>547042</x:v>
+        <x:v>1020173</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1157,28 +1205,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>350000</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1189,28 +1237,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>616386</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1227,22 +1275,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>455146</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1253,28 +1301,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1285,28 +1333,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1323,22 +1371,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1349,28 +1397,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>150000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1387,22 +1435,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>550000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1413,16 +1461,16 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
@@ -1431,10 +1479,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>515838</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1451,10 +1499,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
@@ -1463,10 +1511,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>735613</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1477,16 +1525,16 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
@@ -1495,10 +1543,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1509,28 +1557,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1547,22 +1595,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>511996</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1573,10 +1621,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>80</x:v>
@@ -1585,16 +1633,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>18060379</x:v>
+        <x:v>1019964</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1605,28 +1653,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>1485099</x:v>
+        <x:v>1015019</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1643,22 +1691,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>430866</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1669,28 +1717,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>430866</x:v>
+        <x:v>1019167</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1701,16 +1749,16 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -1719,10 +1767,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>350000</x:v>
+        <x:v>29079466</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1733,10 +1781,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>89</x:v>
@@ -1745,16 +1793,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>506917</x:v>
+        <x:v>1485099</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1771,22 +1819,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>461943</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1797,28 +1845,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>34890</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1835,10 +1883,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -1847,10 +1895,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1867,22 +1915,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>400022</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1899,22 +1947,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>12203100</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1925,10 +1973,10 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>106</x:v>
@@ -1937,16 +1985,16 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>350000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -1957,28 +2005,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F36" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -1989,28 +2037,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>221403</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2027,22 +2075,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>141263</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2059,10 +2107,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>14</x:v>
@@ -2071,10 +2119,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>2250000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2085,28 +2133,28 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
+      <x:c r="E40" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="H40" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2117,16 +2165,16 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
@@ -2135,10 +2183,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>411748</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2155,22 +2203,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>426280</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2181,28 +2229,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>282975</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2213,28 +2261,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2251,22 +2299,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G45" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="H45" s="1">
-        <x:v>487317</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2277,28 +2325,28 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="s">
+      <x:c r="E46" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>300000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2309,65 +2357,257 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>348625</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G48" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H48" s="1">
+        <x:v>1025785</x:v>
+      </x:c>
+      <x:c r="I48" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J48" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G49" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H49" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I49" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J49" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
+      <x:c r="A50" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G50" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H50" s="1">
+        <x:v>487317</x:v>
+      </x:c>
+      <x:c r="I50" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J50" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:10">
+      <x:c r="A51" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
+      <x:c r="B51" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
+      <x:c r="C51" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G51" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H51" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I51" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J51" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:10">
+      <x:c r="A52" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G52" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H52" s="1">
+        <x:v>1015758</x:v>
+      </x:c>
+      <x:c r="I52" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J52" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:10">
+      <x:c r="A53" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F48" s="1" t="s">
+      <x:c r="F53" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H48" s="1">
+      <x:c r="G53" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H53" s="1">
+        <x:v>348625</x:v>
+      </x:c>
+      <x:c r="I53" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:10">
+      <x:c r="A54" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H54" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I48" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J48" s="1" t="s">
+      <x:c r="I54" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J54" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -46,6 +46,30 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2CA31125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGUILAR, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00911610</x:t>
   </x:si>
   <x:si>
@@ -67,9 +91,6 @@
     <x:t>IA</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -82,9 +103,6 @@
     <x:t>BAIRD, JAMES R DR.</x:t>
   </x:si>
   <x:si>
-    <x:t>House</x:t>
-  </x:si>
-  <x:si>
     <x:t>04</x:t>
   </x:si>
   <x:si>
@@ -133,6 +151,18 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
+    <x:t>H4PA13199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOYLE, BRENDAN F</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6OH00163</x:t>
   </x:si>
   <x:si>
@@ -175,6 +205,15 @@
     <x:t>AL</x:t>
   </x:si>
   <x:si>
+    <x:t>H8VA06104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLINE, BENJAMIN LEE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6GA00390</x:t>
   </x:si>
   <x:si>
@@ -193,6 +232,42 @@
     <x:t>35</x:t>
   </x:si>
   <x:si>
+    <x:t>H4MT02098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOWNING, TROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4MN06087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMMER, THOMAS EARL JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0MN07091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FISCHBACH, MICHELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0WI05113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FITZGERALD, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WI</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0GA14030</x:t>
   </x:si>
   <x:si>
@@ -223,12 +298,18 @@
     <x:t>GOODLANDER, MAGGIE</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
     <x:t>NH</x:t>
   </x:si>
   <x:si>
+    <x:t>H6NJ05171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOTTHEIMER, JOSH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>S0SC00149</x:t>
   </x:si>
   <x:si>
@@ -247,6 +328,27 @@
     <x:t>WY</x:t>
   </x:si>
   <x:si>
+    <x:t>H4FL08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HARIDOPOLOS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2NC13243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HARRIGAN, PAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6OK04247</x:t>
   </x:si>
   <x:si>
@@ -289,6 +391,24 @@
     <x:t>HUSTED, JON</x:t>
   </x:si>
   <x:si>
+    <x:t>H4GA03126</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JACK, BRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2IL01349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JACKSON, JONATHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
     <x:t>H2GA01157</x:t>
   </x:si>
   <x:si>
@@ -310,6 +430,27 @@
     <x:t>LA</x:t>
   </x:si>
   <x:si>
+    <x:t>H4OK06056</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS, FRANK D.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8GA06393</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCBATH, LUCIA KAY MS.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0MI10287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCCLAIN, LISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6WA04216</x:t>
   </x:si>
   <x:si>
@@ -325,27 +466,12 @@
     <x:t>MEALER, ALEXANDRA</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>H2NJ13075</x:t>
   </x:si>
   <x:si>
     <x:t>MENENDEZ, ROBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6LA00540</x:t>
   </x:si>
   <x:si>
@@ -373,9 +499,6 @@
     <x:t>MOORE, TIM</x:t>
   </x:si>
   <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6KY00302</x:t>
   </x:si>
   <x:si>
@@ -391,12 +514,36 @@
     <x:t>22</x:t>
   </x:si>
   <x:si>
+    <x:t>H6CA20152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PANETTA, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6TX00388</x:t>
   </x:si>
   <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
   <x:si>
+    <x:t>H0TX11230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PFLUGER, AUGUST LEE II</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8PA18199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RESCHENTHALER, GUY MR.</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6NE00129</x:t>
   </x:si>
   <x:si>
@@ -415,13 +562,34 @@
     <x:t>SD</x:t>
   </x:si>
   <x:si>
+    <x:t>H2NC07096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUZER, DAVID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0MI03316</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCHOLTEN, HILLARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0GA08099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, JAMES AUSTIN</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6TX19206</x:t>
   </x:si>
   <x:si>
     <x:t>SELL, TOM</x:t>
   </x:si>
   <x:si>
-    <x:t>19</x:t>
+    <x:t>H0AL07086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEWELL, TERRI A.</x:t>
   </x:si>
   <x:si>
     <x:t>H6NE03115</x:t>
@@ -430,7 +598,13 @@
     <x:t>SMITH, ADRIAN</x:t>
   </x:si>
   <x:si>
-    <x:t>03</x:t>
+    <x:t>H4MO08162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, JASON T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
   </x:si>
   <x:si>
     <x:t>H8WI01156</x:t>
@@ -439,15 +613,27 @@
     <x:t>STEIL, BRYAN GEORGE</x:t>
   </x:si>
   <x:si>
-    <x:t>WI</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6TX08209</x:t>
   </x:si>
   <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
   </x:si>
   <x:si>
+    <x:t>H4VA10279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUBRAMANYAM, SUHAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8PA05071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, GLENN MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
     <x:t>H8SC04250</x:t>
   </x:si>
   <x:si>
@@ -460,9 +646,6 @@
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
     <x:t>NY</x:t>
   </x:si>
   <x:si>
@@ -475,9 +658,6 @@
     <x:t>45</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6IA00298</x:t>
   </x:si>
   <x:si>
@@ -488,9 +668,6 @@
   </x:si>
   <x:si>
     <x:t>WARNER, MARK ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -561,8 +738,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J54" totalsRowShown="0">
-  <x:autoFilter ref="A1:J54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J79" totalsRowShown="0">
+  <x:autoFilter ref="A1:J79"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -867,7 +1044,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J54"/>
+  <x:dimension ref="A1:J79"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -938,7 +1115,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1">
-        <x:v>69725</x:v>
+        <x:v>512325</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>2026</x:v>
@@ -970,7 +1147,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>513868</x:v>
+        <x:v>69725</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -981,28 +1158,28 @@
     </x:row>
     <x:row r="4" spans="1:10">
       <x:c r="A4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H4" s="1">
-        <x:v>7170138</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>2026</x:v>
@@ -1013,28 +1190,28 @@
     </x:row>
     <x:row r="5" spans="1:10">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H5" s="1">
-        <x:v>628597</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>2026</x:v>
@@ -1045,28 +1222,28 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>508142</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
@@ -1077,28 +1254,28 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>348433</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
@@ -1109,34 +1286,34 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>5731065</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
@@ -1147,60 +1324,60 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1485099</x:v>
+        <x:v>75206</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>1020173</x:v>
+        <x:v>5731065</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
@@ -1220,45 +1397,45 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G11" s="1" t="s">
+      <x:c r="H11" s="1">
+        <x:v>1485099</x:v>
+      </x:c>
+      <x:c r="I11" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="H11" s="1">
-        <x:v>547042</x:v>
-      </x:c>
-      <x:c r="I11" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>350000</x:v>
+        <x:v>1020173</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1269,28 +1446,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>616386</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1301,28 +1478,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>455146</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1333,28 +1510,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>300000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1365,28 +1542,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>708827</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1397,28 +1574,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>91656</x:v>
+        <x:v>74983</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1429,28 +1606,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>150000</x:v>
+        <x:v>76342</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1461,28 +1638,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>550000</x:v>
+        <x:v>76113</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1493,28 +1670,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>515838</x:v>
+        <x:v>74753</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1525,28 +1702,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>735613</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1557,25 +1734,25 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>300000</x:v>
@@ -1589,28 +1766,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>418060</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1621,28 +1798,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="H24" s="1">
-        <x:v>1019964</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1653,28 +1830,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>1015019</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1685,28 +1862,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>511996</x:v>
+        <x:v>512385</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1717,16 +1894,16 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>22</x:v>
@@ -1735,10 +1912,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>1019167</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1749,28 +1926,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>29079466</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1781,28 +1958,28 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>1485099</x:v>
+        <x:v>74932</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1813,28 +1990,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>430866</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1845,28 +2022,28 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>430866</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1877,28 +2054,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1909,28 +2086,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>506917</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1941,28 +2118,28 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>461943</x:v>
+        <x:v>1019964</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1973,28 +2150,28 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>34890</x:v>
+        <x:v>1015019</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -2005,28 +2182,28 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C36" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>250000</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2037,28 +2214,28 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>400022</x:v>
+        <x:v>1019167</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2069,28 +2246,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>12203100</x:v>
+        <x:v>29079466</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2101,28 +2278,28 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>350000</x:v>
+        <x:v>1485099</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2133,28 +2310,28 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>80948</x:v>
+        <x:v>74699</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2165,28 +2342,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>221403</x:v>
+        <x:v>75227</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2197,28 +2374,28 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>141263</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2229,28 +2406,28 @@
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H43" s="1">
-        <x:v>2250000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>2026</x:v>
@@ -2261,25 +2438,25 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H44" s="1">
         <x:v>350000</x:v>
@@ -2293,28 +2470,28 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>411748</x:v>
+        <x:v>74602</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2325,28 +2502,28 @@
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>426280</x:v>
+        <x:v>76114</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2357,28 +2534,28 @@
     </x:row>
     <x:row r="47" spans="1:10">
       <x:c r="A47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>282975</x:v>
+        <x:v>75226</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2389,28 +2566,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>1025785</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2421,28 +2598,28 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>771658</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2453,28 +2630,28 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>487317</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>2026</x:v>
@@ -2485,28 +2662,28 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>300000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2517,28 +2694,28 @@
     </x:row>
     <x:row r="52" spans="1:10">
       <x:c r="A52" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>1015758</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>
@@ -2549,65 +2726,865 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H53" s="1">
-        <x:v>348625</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I53" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J53" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:10">
       <x:c r="A54" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G54" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H54" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I54" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J54" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:10">
+      <x:c r="A55" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H55" s="1">
+        <x:v>80948</x:v>
+      </x:c>
+      <x:c r="I55" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J55" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:10">
+      <x:c r="A56" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G56" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H56" s="1">
+        <x:v>221403</x:v>
+      </x:c>
+      <x:c r="I56" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J56" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:10">
+      <x:c r="A57" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G57" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H57" s="1">
+        <x:v>141263</x:v>
+      </x:c>
+      <x:c r="I57" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J57" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:10">
+      <x:c r="A58" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F58" s="1" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H58" s="1">
+        <x:v>74692</x:v>
+      </x:c>
+      <x:c r="I58" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J58" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:10">
+      <x:c r="A59" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F59" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G59" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H59" s="1">
+        <x:v>2250000</x:v>
+      </x:c>
+      <x:c r="I59" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J59" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:10">
+      <x:c r="A60" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F60" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G60" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H60" s="1">
+        <x:v>75000</x:v>
+      </x:c>
+      <x:c r="I60" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J60" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:10">
+      <x:c r="A61" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G61" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H61" s="1">
+        <x:v>75844</x:v>
+      </x:c>
+      <x:c r="I61" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J61" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:10">
+      <x:c r="A62" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="E62" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F62" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G62" s="1" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H62" s="1">
+        <x:v>350000</x:v>
+      </x:c>
+      <x:c r="I62" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J62" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:10">
+      <x:c r="A63" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D63" s="1" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="E63" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F63" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G63" s="1" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H63" s="1">
+        <x:v>411748</x:v>
+      </x:c>
+      <x:c r="I63" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J63" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:10">
+      <x:c r="A64" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F64" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G64" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H64" s="1">
+        <x:v>75320</x:v>
+      </x:c>
+      <x:c r="I64" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J64" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:10">
+      <x:c r="A65" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="E65" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F65" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G65" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H65" s="1">
+        <x:v>74382</x:v>
+      </x:c>
+      <x:c r="I65" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J65" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:10">
+      <x:c r="A66" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B66" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="E66" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F66" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G66" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H66" s="1">
+        <x:v>75281</x:v>
+      </x:c>
+      <x:c r="I66" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J66" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:10">
+      <x:c r="A67" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B67" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="E67" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F67" s="1" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G67" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H67" s="1">
+        <x:v>426280</x:v>
+      </x:c>
+      <x:c r="I67" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J67" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:10">
+      <x:c r="A68" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="E68" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F68" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G68" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H68" s="1">
+        <x:v>74852</x:v>
+      </x:c>
+      <x:c r="I68" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J68" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:10">
+      <x:c r="A69" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B69" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="E69" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F69" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G69" s="1" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H69" s="1">
+        <x:v>282975</x:v>
+      </x:c>
+      <x:c r="I69" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J69" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:10">
+      <x:c r="A70" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B70" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D70" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E70" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F70" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G70" s="1" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H70" s="1">
+        <x:v>75617</x:v>
+      </x:c>
+      <x:c r="I70" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J70" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:10">
+      <x:c r="A71" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B71" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="E71" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F71" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G71" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H71" s="1">
+        <x:v>1025785</x:v>
+      </x:c>
+      <x:c r="I71" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J71" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:10">
+      <x:c r="A72" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B72" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C72" s="1" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D72" s="1" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E72" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F72" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G72" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H72" s="1">
+        <x:v>771658</x:v>
+      </x:c>
+      <x:c r="I72" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J72" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:10">
+      <x:c r="A73" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B73" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="E73" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F73" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G73" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H73" s="1">
+        <x:v>75332</x:v>
+      </x:c>
+      <x:c r="I73" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J73" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:10">
+      <x:c r="A74" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D74" s="1" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="E74" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F74" s="1" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G74" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H74" s="1">
+        <x:v>73673</x:v>
+      </x:c>
+      <x:c r="I74" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J74" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:10">
+      <x:c r="A75" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B75" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C75" s="1" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D75" s="1" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="E75" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F75" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B54" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C54" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="E54" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F54" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G54" s="1" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H54" s="1">
+      <x:c r="G75" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H75" s="1">
+        <x:v>487317</x:v>
+      </x:c>
+      <x:c r="I75" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J75" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:10">
+      <x:c r="A76" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B76" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C76" s="1" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D76" s="1" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="E76" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F76" s="1" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G76" s="1" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H76" s="1">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="I76" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J76" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:10">
+      <x:c r="A77" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="E77" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F77" s="1" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G77" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H77" s="1">
+        <x:v>1015758</x:v>
+      </x:c>
+      <x:c r="I77" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J77" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:10">
+      <x:c r="A78" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B78" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C78" s="1" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="E78" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F78" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G78" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H78" s="1">
+        <x:v>348625</x:v>
+      </x:c>
+      <x:c r="I78" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J78" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:10">
+      <x:c r="A79" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B79" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C79" s="1" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D79" s="1" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="E79" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F79" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G79" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H79" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I54" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J54" s="1" t="s">
+      <x:c r="I79" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J79" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1403,7 +1403,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1485099</x:v>
+        <x:v>3465231</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -2299,7 +2299,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>1485099</x:v>
+        <x:v>2475165</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1147,7 +1147,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>69725</x:v>
+        <x:v>145696</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -3547,7 +3547,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>348625</x:v>
+        <x:v>424596</x:v>
       </x:c>
       <x:c r="I78" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -514,6 +514,15 @@
     <x:t>22</x:t>
   </x:si>
   <x:si>
+    <x:t>S4NE00207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSBORN, DAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6CA20152</x:t>
   </x:si>
   <x:si>
@@ -548,9 +557,6 @@
   </x:si>
   <x:si>
     <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
   </x:si>
   <x:si>
     <x:t>S4SD00049</x:t>
@@ -738,8 +744,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J79" totalsRowShown="0">
-  <x:autoFilter ref="A1:J79"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J80" totalsRowShown="0">
+  <x:autoFilter ref="A1:J80"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -1044,7 +1050,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J79"/>
+  <x:dimension ref="A1:J80"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1371,7 +1377,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>5731065</x:v>
+        <x:v>12894063</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -2267,7 +2273,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>29079466</x:v>
+        <x:v>33778233</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2886,10 +2892,10 @@
     </x:row>
     <x:row r="58" spans="1:10">
       <x:c r="A58" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>166</x:v>
@@ -2898,30 +2904,30 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G58" s="1" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G58" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H58" s="1">
-        <x:v>74692</x:v>
+        <x:v>6723910</x:v>
       </x:c>
       <x:c r="I58" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>169</x:v>
@@ -2930,16 +2936,16 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H59" s="1">
-        <x:v>2250000</x:v>
+        <x:v>74692</x:v>
       </x:c>
       <x:c r="I59" s="1">
         <x:v>2026</x:v>
@@ -2950,28 +2956,28 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>75000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I60" s="1">
         <x:v>2026</x:v>
@@ -2997,13 +3003,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H61" s="1">
-        <x:v>75844</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I61" s="1">
         <x:v>2026</x:v>
@@ -3014,28 +3020,28 @@
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>350000</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="I62" s="1">
         <x:v>2026</x:v>
@@ -3046,10 +3052,10 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>179</x:v>
@@ -3064,10 +3070,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H63" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I63" s="1">
         <x:v>2026</x:v>
@@ -3084,22 +3090,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D64" s="1" t="s">
+      <x:c r="E64" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F64" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G64" s="1" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="E64" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F64" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G64" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="H64" s="1">
-        <x:v>75320</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I64" s="1">
         <x:v>2026</x:v>
@@ -3110,10 +3116,10 @@
     </x:row>
     <x:row r="65" spans="1:10">
       <x:c r="A65" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>184</x:v>
@@ -3125,13 +3131,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H65" s="1">
-        <x:v>74382</x:v>
+        <x:v>75320</x:v>
       </x:c>
       <x:c r="I65" s="1">
         <x:v>2026</x:v>
@@ -3142,10 +3148,10 @@
     </x:row>
     <x:row r="66" spans="1:10">
       <x:c r="A66" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>186</x:v>
@@ -3157,13 +3163,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H66" s="1">
-        <x:v>75281</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="I66" s="1">
         <x:v>2026</x:v>
@@ -3189,13 +3195,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H67" s="1">
-        <x:v>426280</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="I67" s="1">
         <x:v>2026</x:v>
@@ -3206,10 +3212,10 @@
     </x:row>
     <x:row r="68" spans="1:10">
       <x:c r="A68" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>190</x:v>
@@ -3221,13 +3227,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>74852</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I68" s="1">
         <x:v>2026</x:v>
@@ -3238,10 +3244,10 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>192</x:v>
@@ -3253,13 +3259,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>282975</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="I69" s="1">
         <x:v>2026</x:v>
@@ -3285,13 +3291,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>75617</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I70" s="1">
         <x:v>2026</x:v>
@@ -3302,28 +3308,28 @@
     </x:row>
     <x:row r="71" spans="1:10">
       <x:c r="A71" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D71" s="1" t="s">
+      <x:c r="E71" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F71" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G71" s="1" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="E71" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F71" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G71" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="H71" s="1">
-        <x:v>1025785</x:v>
+        <x:v>75617</x:v>
       </x:c>
       <x:c r="I71" s="1">
         <x:v>2026</x:v>
@@ -3334,10 +3340,10 @@
     </x:row>
     <x:row r="72" spans="1:10">
       <x:c r="A72" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>199</x:v>
@@ -3349,13 +3355,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>771658</x:v>
+        <x:v>1025785</x:v>
       </x:c>
       <x:c r="I72" s="1">
         <x:v>2026</x:v>
@@ -3366,10 +3372,10 @@
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
         <x:v>201</x:v>
@@ -3381,13 +3387,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>75332</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I73" s="1">
         <x:v>2026</x:v>
@@ -3398,10 +3404,10 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>203</x:v>
@@ -3413,13 +3419,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>73673</x:v>
+        <x:v>75332</x:v>
       </x:c>
       <x:c r="I74" s="1">
         <x:v>2026</x:v>
@@ -3436,22 +3442,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D75" s="1" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D75" s="1" t="s">
+      <x:c r="E75" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F75" s="1" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="E75" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F75" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>487317</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="I75" s="1">
         <x:v>2026</x:v>
@@ -3462,10 +3468,10 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>208</x:v>
@@ -3477,13 +3483,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>300000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I76" s="1">
         <x:v>2026</x:v>
@@ -3494,28 +3500,28 @@
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="D77" s="1" t="s">
+      <x:c r="E77" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F77" s="1" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G77" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="E77" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F77" s="1" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G77" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H77" s="1">
-        <x:v>1015758</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I77" s="1">
         <x:v>2026</x:v>
@@ -3526,42 +3532,42 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="D78" s="1" t="s">
+      <x:c r="E78" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F78" s="1" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="E78" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F78" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>424596</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="I78" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J78" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>216</x:v>
@@ -3576,15 +3582,47 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H79" s="1">
+        <x:v>424596</x:v>
+      </x:c>
+      <x:c r="I79" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J79" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:10">
+      <x:c r="A80" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B80" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C80" s="1" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D80" s="1" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E80" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F80" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G80" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H79" s="1">
+      <x:c r="H80" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I79" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J79" s="1" t="s">
+      <x:c r="I80" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J80" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -668,6 +668,12 @@
   </x:si>
   <x:si>
     <x:t>TUREK, JOSHUA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0CA15213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
   </x:si>
   <x:si>
     <x:t>S6VA00093</x:t>
@@ -744,8 +750,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J80" totalsRowShown="0">
-  <x:autoFilter ref="A1:J80"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J81" totalsRowShown="0">
+  <x:autoFilter ref="A1:J81"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -1050,7 +1056,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J80"/>
+  <x:dimension ref="A1:J81"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3596,10 +3602,10 @@
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>218</x:v>
@@ -3608,21 +3614,53 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F80" s="1" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G80" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H80" s="1">
+        <x:v>362000</x:v>
+      </x:c>
+      <x:c r="I80" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J80" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:10">
+      <x:c r="A81" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F80" s="1" t="s">
+      <x:c r="F81" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G80" s="1" t="s">
+      <x:c r="G81" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H80" s="1">
+      <x:c r="H81" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I80" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J80" s="1" t="s">
+      <x:c r="I81" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J81" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -629,6 +629,12 @@
   </x:si>
   <x:si>
     <x:t>SUBRAMANYAM, SUHAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6TX00479</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TALARICO, JAMES</x:t>
   </x:si>
   <x:si>
     <x:t>H8PA05071</x:t>
@@ -750,8 +756,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J81" totalsRowShown="0">
-  <x:autoFilter ref="A1:J81"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J83" totalsRowShown="0">
+  <x:autoFilter ref="A1:J83"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -1056,7 +1062,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J81"/>
+  <x:dimension ref="A1:J83"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1159,7 +1165,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>145696</x:v>
+        <x:v>145958</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -1415,7 +1421,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>3465231</x:v>
+        <x:v>3507184</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -2311,7 +2317,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>2475165</x:v>
+        <x:v>2477373</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2962,10 +2968,10 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>172</x:v>
@@ -2983,7 +2989,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>2250000</x:v>
+        <x:v>4075</x:v>
       </x:c>
       <x:c r="I60" s="1">
         <x:v>2026</x:v>
@@ -2994,28 +3000,28 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="H61" s="1">
-        <x:v>75000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I61" s="1">
         <x:v>2026</x:v>
@@ -3032,22 +3038,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>75844</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="I62" s="1">
         <x:v>2026</x:v>
@@ -3058,28 +3064,28 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H63" s="1">
-        <x:v>350000</x:v>
+        <x:v>75844</x:v>
       </x:c>
       <x:c r="I63" s="1">
         <x:v>2026</x:v>
@@ -3090,16 +3096,16 @@
     </x:row>
     <x:row r="64" spans="1:10">
       <x:c r="A64" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>22</x:v>
@@ -3108,10 +3114,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H64" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I64" s="1">
         <x:v>2026</x:v>
@@ -3128,22 +3134,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H65" s="1">
-        <x:v>75320</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I65" s="1">
         <x:v>2026</x:v>
@@ -3154,28 +3160,28 @@
     </x:row>
     <x:row r="66" spans="1:10">
       <x:c r="A66" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H66" s="1">
-        <x:v>74382</x:v>
+        <x:v>75320</x:v>
       </x:c>
       <x:c r="I66" s="1">
         <x:v>2026</x:v>
@@ -3186,28 +3192,28 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H67" s="1">
-        <x:v>75281</x:v>
+        <x:v>74382</x:v>
       </x:c>
       <x:c r="I67" s="1">
         <x:v>2026</x:v>
@@ -3224,22 +3230,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>426280</x:v>
+        <x:v>75281</x:v>
       </x:c>
       <x:c r="I68" s="1">
         <x:v>2026</x:v>
@@ -3250,28 +3256,28 @@
     </x:row>
     <x:row r="69" spans="1:10">
       <x:c r="A69" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>74852</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I69" s="1">
         <x:v>2026</x:v>
@@ -3282,28 +3288,28 @@
     </x:row>
     <x:row r="70" spans="1:10">
       <x:c r="A70" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>282975</x:v>
+        <x:v>74852</x:v>
       </x:c>
       <x:c r="I70" s="1">
         <x:v>2026</x:v>
@@ -3320,22 +3326,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>75617</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I71" s="1">
         <x:v>2026</x:v>
@@ -3346,28 +3352,28 @@
     </x:row>
     <x:row r="72" spans="1:10">
       <x:c r="A72" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>1025785</x:v>
+        <x:v>75617</x:v>
       </x:c>
       <x:c r="I72" s="1">
         <x:v>2026</x:v>
@@ -3378,28 +3384,28 @@
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>771658</x:v>
+        <x:v>1025785</x:v>
       </x:c>
       <x:c r="I73" s="1">
         <x:v>2026</x:v>
@@ -3410,28 +3416,28 @@
     </x:row>
     <x:row r="74" spans="1:10">
       <x:c r="A74" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>75332</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I74" s="1">
         <x:v>2026</x:v>
@@ -3442,28 +3448,28 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>73673</x:v>
+        <x:v>75332</x:v>
       </x:c>
       <x:c r="I75" s="1">
         <x:v>2026</x:v>
@@ -3474,60 +3480,60 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>487317</x:v>
+        <x:v>77424</x:v>
       </x:c>
       <x:c r="I76" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:10">
       <x:c r="A77" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>300000</x:v>
+        <x:v>73673</x:v>
       </x:c>
       <x:c r="I77" s="1">
         <x:v>2026</x:v>
@@ -3538,28 +3544,28 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>1015758</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I78" s="1">
         <x:v>2026</x:v>
@@ -3570,60 +3576,60 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H79" s="1">
-        <x:v>424596</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I79" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H80" s="1">
-        <x:v>362000</x:v>
+        <x:v>1015758</x:v>
       </x:c>
       <x:c r="I80" s="1">
         <x:v>2026</x:v>
@@ -3634,16 +3640,16 @@
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
         <x:v>22</x:v>
@@ -3652,15 +3658,79 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H81" s="1">
+        <x:v>429577</x:v>
+      </x:c>
+      <x:c r="I81" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J81" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:10">
+      <x:c r="A82" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C82" s="1" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="E82" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F82" s="1" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G82" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H82" s="1">
+        <x:v>381352</x:v>
+      </x:c>
+      <x:c r="I82" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J82" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:10">
+      <x:c r="A83" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="E83" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F83" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G83" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H81" s="1">
+      <x:c r="H83" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I81" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J81" s="1" t="s">
+      <x:c r="I83" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J83" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1357,7 +1357,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>75206</x:v>
+        <x:v>150412</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1389,7 +1389,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>12894063</x:v>
+        <x:v>19706265</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1517,7 +1517,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1613,7 +1613,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>74983</x:v>
+        <x:v>149966</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>76342</x:v>
+        <x:v>152684</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1677,7 +1677,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>76113</x:v>
+        <x:v>152226</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>74753</x:v>
+        <x:v>149506</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1997,7 +1997,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>74932</x:v>
+        <x:v>149864</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -2029,7 +2029,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -2285,7 +2285,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>33778233</x:v>
+        <x:v>36054435</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2349,7 +2349,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>74699</x:v>
+        <x:v>149398</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2381,7 +2381,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>75227</x:v>
+        <x:v>150454</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>74602</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>76114</x:v>
+        <x:v>152228</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2573,7 +2573,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>75226</x:v>
+        <x:v>150452</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2925,7 +2925,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="H58" s="1">
-        <x:v>6723910</x:v>
+        <x:v>10825942</x:v>
       </x:c>
       <x:c r="I58" s="1">
         <x:v>2026</x:v>
@@ -2957,7 +2957,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H59" s="1">
-        <x:v>74692</x:v>
+        <x:v>149384</x:v>
       </x:c>
       <x:c r="I59" s="1">
         <x:v>2026</x:v>
@@ -3053,7 +3053,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>75000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I62" s="1">
         <x:v>2026</x:v>
@@ -3085,7 +3085,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H63" s="1">
-        <x:v>75844</x:v>
+        <x:v>151688</x:v>
       </x:c>
       <x:c r="I63" s="1">
         <x:v>2026</x:v>
@@ -3181,7 +3181,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H66" s="1">
-        <x:v>75320</x:v>
+        <x:v>150604</x:v>
       </x:c>
       <x:c r="I66" s="1">
         <x:v>2026</x:v>
@@ -3213,7 +3213,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H67" s="1">
-        <x:v>74382</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="I67" s="1">
         <x:v>2026</x:v>
@@ -3245,7 +3245,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>75281</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="I68" s="1">
         <x:v>2026</x:v>
@@ -3309,7 +3309,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>74852</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="I70" s="1">
         <x:v>2026</x:v>
@@ -3373,7 +3373,7 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>75617</x:v>
+        <x:v>151234</x:v>
       </x:c>
       <x:c r="I72" s="1">
         <x:v>2026</x:v>
@@ -3469,7 +3469,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>75332</x:v>
+        <x:v>150664</x:v>
       </x:c>
       <x:c r="I75" s="1">
         <x:v>2026</x:v>
@@ -3533,7 +3533,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>73673</x:v>
+        <x:v>147346</x:v>
       </x:c>
       <x:c r="I77" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1165,7 +1165,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>145958</x:v>
+        <x:v>146187</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>3507184</x:v>
+        <x:v>4040310</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>2477373</x:v>
+        <x:v>2974411</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2989,7 +2989,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>4075</x:v>
+        <x:v>40704</x:v>
       </x:c>
       <x:c r="I60" s="1">
         <x:v>2026</x:v>
@@ -3501,7 +3501,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>77424</x:v>
+        <x:v>114053</x:v>
       </x:c>
       <x:c r="I76" s="1">
         <x:v>2026</x:v>
@@ -3661,7 +3661,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>429577</x:v>
+        <x:v>433936</x:v>
       </x:c>
       <x:c r="I81" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1165,7 +1165,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>146187</x:v>
+        <x:v>146408</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -3661,7 +3661,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>433936</x:v>
+        <x:v>438132</x:v>
       </x:c>
       <x:c r="I81" s="1">
         <x:v>2026</x:v>
@@ -3693,7 +3693,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>381352</x:v>
+        <x:v>432714</x:v>
       </x:c>
       <x:c r="I82" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -1165,7 +1165,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="1">
-        <x:v>146408</x:v>
+        <x:v>165925</x:v>
       </x:c>
       <x:c r="I3" s="1">
         <x:v>2026</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4040310</x:v>
+        <x:v>4229538</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>2974411</x:v>
+        <x:v>3020793</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2989,7 +2989,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>40704</x:v>
+        <x:v>165588</x:v>
       </x:c>
       <x:c r="I60" s="1">
         <x:v>2026</x:v>
@@ -3501,7 +3501,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>114053</x:v>
+        <x:v>392890</x:v>
       </x:c>
       <x:c r="I76" s="1">
         <x:v>2026</x:v>
@@ -3661,7 +3661,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>438132</x:v>
+        <x:v>474362</x:v>
       </x:c>
       <x:c r="I81" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -3693,7 +3693,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>432714</x:v>
+        <x:v>484076</x:v>
       </x:c>
       <x:c r="I82" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -2285,7 +2285,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>36054435</x:v>
+        <x:v>36874167</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2925,7 +2925,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="H58" s="1">
-        <x:v>10825942</x:v>
+        <x:v>13476278</x:v>
       </x:c>
       <x:c r="I58" s="1">
         <x:v>2026</x:v>
@@ -3693,7 +3693,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>484076</x:v>
+        <x:v>535438</x:v>
       </x:c>
       <x:c r="I82" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-F24-ie-report.xlsx
@@ -250,6 +250,18 @@
     <x:t>MN</x:t>
   </x:si>
   <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4AL02170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIGURES, SHOMARI C.</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0MN07091</x:t>
   </x:si>
   <x:si>
@@ -421,6 +433,15 @@
     <x:t>KINGSTON, JAMES MORRIS</x:t>
   </x:si>
   <x:si>
+    <x:t>H6OH15112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEONARD, DON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6LA00664</x:t>
   </x:si>
   <x:si>
@@ -436,6 +457,12 @@
     <x:t>LUCAS, FRANK D.</x:t>
   </x:si>
   <x:si>
+    <x:t>H6AL01086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARQUES, RHETT</x:t>
+  </x:si>
+  <x:si>
     <x:t>H8GA06393</x:t>
   </x:si>
   <x:si>
@@ -641,9 +668,6 @@
   </x:si>
   <x:si>
     <x:t>THOMPSON, GLENN MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>H8SC04250</x:t>
@@ -756,8 +780,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J83" totalsRowShown="0">
-  <x:autoFilter ref="A1:J83"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J86" totalsRowShown="0">
+  <x:autoFilter ref="A1:J86"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -1062,12 +1086,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J83"/>
+  <x:dimension ref="A1:J86"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="23.424911" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="24.282054" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="14.853482" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="30.996339" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="17.853482" style="1" customWidth="1"/>
@@ -1656,34 +1680,34 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>152226</x:v>
+        <x:v>101595</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
@@ -1694,22 +1718,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>149506</x:v>
+        <x:v>152226</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1726,22 +1750,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>455146</x:v>
+        <x:v>149506</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1752,28 +1776,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>300000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1784,28 +1808,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1822,22 +1846,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>91656</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1848,28 +1872,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>150000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1880,28 +1904,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>512385</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1912,28 +1936,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>550000</x:v>
+        <x:v>512385</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1944,16 +1968,16 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>22</x:v>
@@ -1962,10 +1986,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>515838</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1982,22 +2006,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>149864</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -2023,13 +2047,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>150000</x:v>
+        <x:v>149864</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -2046,22 +2070,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>735613</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -2072,16 +2096,16 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>22</x:v>
@@ -2090,10 +2114,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>300000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -2104,28 +2128,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>418060</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -2136,16 +2160,16 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>14</x:v>
@@ -2154,10 +2178,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>1019964</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -2174,22 +2198,22 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>1015019</x:v>
+        <x:v>1019964</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
@@ -2200,16 +2224,16 @@
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>14</x:v>
@@ -2218,10 +2242,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="1">
-        <x:v>511996</x:v>
+        <x:v>1015019</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>2026</x:v>
@@ -2232,16 +2256,16 @@
     </x:row>
     <x:row r="37" spans="1:10">
       <x:c r="A37" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>14</x:v>
@@ -2250,10 +2274,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H37" s="1">
-        <x:v>1019167</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>2026</x:v>
@@ -2264,28 +2288,28 @@
     </x:row>
     <x:row r="38" spans="1:10">
       <x:c r="A38" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H38" s="1">
-        <x:v>36874167</x:v>
+        <x:v>1019167</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>2026</x:v>
@@ -2296,16 +2320,16 @@
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>22</x:v>
@@ -2317,7 +2341,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H39" s="1">
-        <x:v>3020793</x:v>
+        <x:v>36874167</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>2026</x:v>
@@ -2328,28 +2352,28 @@
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H40" s="1">
-        <x:v>149398</x:v>
+        <x:v>3020793</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>2026</x:v>
@@ -2360,28 +2384,28 @@
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H41" s="1">
-        <x:v>150454</x:v>
+        <x:v>149398</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>2026</x:v>
@@ -2392,16 +2416,16 @@
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>14</x:v>
@@ -2410,10 +2434,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H42" s="1">
-        <x:v>430866</x:v>
+        <x:v>150454</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>2026</x:v>
@@ -2430,10 +2454,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>14</x:v>
@@ -2456,28 +2480,28 @@
     </x:row>
     <x:row r="44" spans="1:10">
       <x:c r="A44" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H44" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>2026</x:v>
@@ -2488,60 +2512,60 @@
     </x:row>
     <x:row r="45" spans="1:10">
       <x:c r="A45" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H45" s="1">
-        <x:v>149204</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="I45" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
       <x:c r="A46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H46" s="1">
-        <x:v>152228</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I46" s="1">
         <x:v>2026</x:v>
@@ -2558,22 +2582,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H47" s="1">
-        <x:v>150452</x:v>
+        <x:v>149204</x:v>
       </x:c>
       <x:c r="I47" s="1">
         <x:v>2026</x:v>
@@ -2584,28 +2608,28 @@
     </x:row>
     <x:row r="48" spans="1:10">
       <x:c r="A48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H48" s="1">
-        <x:v>506917</x:v>
+        <x:v>101595</x:v>
       </x:c>
       <x:c r="I48" s="1">
         <x:v>2026</x:v>
@@ -2616,28 +2640,28 @@
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H49" s="1">
-        <x:v>461943</x:v>
+        <x:v>152228</x:v>
       </x:c>
       <x:c r="I49" s="1">
         <x:v>2026</x:v>
@@ -2648,28 +2672,28 @@
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H50" s="1">
-        <x:v>34890</x:v>
+        <x:v>150452</x:v>
       </x:c>
       <x:c r="I50" s="1">
         <x:v>2026</x:v>
@@ -2680,28 +2704,28 @@
     </x:row>
     <x:row r="51" spans="1:10">
       <x:c r="A51" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H51" s="1">
-        <x:v>250000</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="I51" s="1">
         <x:v>2026</x:v>
@@ -2718,22 +2742,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H52" s="1">
-        <x:v>400022</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="I52" s="1">
         <x:v>2026</x:v>
@@ -2744,28 +2768,28 @@
     </x:row>
     <x:row r="53" spans="1:10">
       <x:c r="A53" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H53" s="1">
-        <x:v>12203100</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="I53" s="1">
         <x:v>2026</x:v>
@@ -2782,10 +2806,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>22</x:v>
@@ -2794,10 +2818,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H54" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="I54" s="1">
         <x:v>2026</x:v>
@@ -2814,22 +2838,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H55" s="1">
-        <x:v>80948</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="I55" s="1">
         <x:v>2026</x:v>
@@ -2840,16 +2864,16 @@
     </x:row>
     <x:row r="56" spans="1:10">
       <x:c r="A56" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>22</x:v>
@@ -2858,10 +2882,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H56" s="1">
-        <x:v>221403</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="I56" s="1">
         <x:v>2026</x:v>
@@ -2872,28 +2896,28 @@
     </x:row>
     <x:row r="57" spans="1:10">
       <x:c r="A57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H57" s="1">
-        <x:v>141263</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I57" s="1">
         <x:v>2026</x:v>
@@ -2910,54 +2934,54 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H58" s="1">
-        <x:v>13476278</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="I58" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:10">
       <x:c r="A59" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H59" s="1">
-        <x:v>149384</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="I59" s="1">
         <x:v>2026</x:v>
@@ -2968,10 +2992,10 @@
     </x:row>
     <x:row r="60" spans="1:10">
       <x:c r="A60" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>172</x:v>
@@ -2980,16 +3004,16 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="H60" s="1">
-        <x:v>165588</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="I60" s="1">
         <x:v>2026</x:v>
@@ -3000,16 +3024,16 @@
     </x:row>
     <x:row r="61" spans="1:10">
       <x:c r="A61" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>22</x:v>
@@ -3018,42 +3042,42 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H61" s="1">
-        <x:v>2250000</x:v>
+        <x:v>13476278</x:v>
       </x:c>
       <x:c r="I61" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J61" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:10">
       <x:c r="A62" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H62" s="1">
-        <x:v>150000</x:v>
+        <x:v>149384</x:v>
       </x:c>
       <x:c r="I62" s="1">
         <x:v>2026</x:v>
@@ -3064,28 +3088,28 @@
     </x:row>
     <x:row r="63" spans="1:10">
       <x:c r="A63" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H63" s="1">
-        <x:v>151688</x:v>
+        <x:v>165588</x:v>
       </x:c>
       <x:c r="I63" s="1">
         <x:v>2026</x:v>
@@ -3102,10 +3126,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>22</x:v>
@@ -3114,10 +3138,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H64" s="1">
-        <x:v>350000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="I64" s="1">
         <x:v>2026</x:v>
@@ -3134,22 +3158,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H65" s="1">
-        <x:v>411748</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="I65" s="1">
         <x:v>2026</x:v>
@@ -3166,22 +3190,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H66" s="1">
-        <x:v>150604</x:v>
+        <x:v>151688</x:v>
       </x:c>
       <x:c r="I66" s="1">
         <x:v>2026</x:v>
@@ -3192,28 +3216,28 @@
     </x:row>
     <x:row r="67" spans="1:10">
       <x:c r="A67" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H67" s="1">
-        <x:v>148764</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="I67" s="1">
         <x:v>2026</x:v>
@@ -3230,22 +3254,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H68" s="1">
-        <x:v>150562</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="I68" s="1">
         <x:v>2026</x:v>
@@ -3262,22 +3286,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H69" s="1">
-        <x:v>426280</x:v>
+        <x:v>150604</x:v>
       </x:c>
       <x:c r="I69" s="1">
         <x:v>2026</x:v>
@@ -3294,22 +3318,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H70" s="1">
-        <x:v>149704</x:v>
+        <x:v>148764</x:v>
       </x:c>
       <x:c r="I70" s="1">
         <x:v>2026</x:v>
@@ -3326,22 +3350,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H71" s="1">
-        <x:v>282975</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="I71" s="1">
         <x:v>2026</x:v>
@@ -3358,22 +3382,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H72" s="1">
-        <x:v>151234</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="I72" s="1">
         <x:v>2026</x:v>
@@ -3384,28 +3408,28 @@
     </x:row>
     <x:row r="73" spans="1:10">
       <x:c r="A73" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H73" s="1">
-        <x:v>1025785</x:v>
+        <x:v>149704</x:v>
       </x:c>
       <x:c r="I73" s="1">
         <x:v>2026</x:v>
@@ -3422,22 +3446,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H74" s="1">
-        <x:v>771658</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="I74" s="1">
         <x:v>2026</x:v>
@@ -3448,28 +3472,28 @@
     </x:row>
     <x:row r="75" spans="1:10">
       <x:c r="A75" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H75" s="1">
-        <x:v>150664</x:v>
+        <x:v>151234</x:v>
       </x:c>
       <x:c r="I75" s="1">
         <x:v>2026</x:v>
@@ -3480,34 +3504,34 @@
     </x:row>
     <x:row r="76" spans="1:10">
       <x:c r="A76" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H76" s="1">
-        <x:v>392890</x:v>
+        <x:v>1025785</x:v>
       </x:c>
       <x:c r="I76" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J76" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:10">
@@ -3518,22 +3542,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H77" s="1">
-        <x:v>147346</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="I77" s="1">
         <x:v>2026</x:v>
@@ -3544,28 +3568,28 @@
     </x:row>
     <x:row r="78" spans="1:10">
       <x:c r="A78" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H78" s="1">
-        <x:v>487317</x:v>
+        <x:v>150664</x:v>
       </x:c>
       <x:c r="I78" s="1">
         <x:v>2026</x:v>
@@ -3576,60 +3600,60 @@
     </x:row>
     <x:row r="79" spans="1:10">
       <x:c r="A79" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H79" s="1">
-        <x:v>300000</x:v>
+        <x:v>392890</x:v>
       </x:c>
       <x:c r="I79" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J79" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:10">
       <x:c r="A80" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H80" s="1">
-        <x:v>1015758</x:v>
+        <x:v>147346</x:v>
       </x:c>
       <x:c r="I80" s="1">
         <x:v>2026</x:v>
@@ -3640,10 +3664,10 @@
     </x:row>
     <x:row r="81" spans="1:10">
       <x:c r="A81" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
         <x:v>218</x:v>
@@ -3652,30 +3676,30 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H81" s="1">
-        <x:v>474362</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="I81" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J81" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:10">
       <x:c r="A82" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>220</x:v>
@@ -3687,13 +3711,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H82" s="1">
-        <x:v>535438</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="I82" s="1">
         <x:v>2026</x:v>
@@ -3704,33 +3728,129 @@
     </x:row>
     <x:row r="83" spans="1:10">
       <x:c r="A83" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="E83" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F83" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G83" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H83" s="1">
+        <x:v>1015758</x:v>
+      </x:c>
+      <x:c r="I83" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J83" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:10">
+      <x:c r="A84" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B84" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C84" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="E84" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F84" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G84" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H84" s="1">
+        <x:v>474362</x:v>
+      </x:c>
+      <x:c r="I84" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J84" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:10">
+      <x:c r="A85" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B85" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C85" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D85" s="1" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="E85" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F85" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G85" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H85" s="1">
+        <x:v>535438</x:v>
+      </x:c>
+      <x:c r="I85" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J85" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:10">
+      <x:c r="A86" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B83" s="1" t="s">
+      <x:c r="B86" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C83" s="1" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D83" s="1" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="E83" s="1" t="s">
+      <x:c r="C86" s="1" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D86" s="1" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="E86" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F83" s="1" t="s">
+      <x:c r="F86" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G83" s="1" t="s">
+      <x:c r="G86" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H83" s="1">
+      <x:c r="H86" s="1">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I83" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J83" s="1" t="s">
+      <x:c r="I86" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J86" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
